--- a/Result/profitability/2008.xlsx
+++ b/Result/profitability/2008.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.13</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1287499999999998</v>
+        <v>0.1362499999999998</v>
       </c>
       <c r="N2" t="n">
-        <v>15.1975</v>
+        <v>15.3375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.21</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2599999999999998</v>
+        <v>0.2974999999999998</v>
       </c>
       <c r="N3" t="n">
-        <v>15.51875</v>
+        <v>16.07875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.57</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3412499999999998</v>
+        <v>0.3612499999999997</v>
       </c>
       <c r="N4" t="n">
-        <v>15.77875</v>
+        <v>15.805</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-2.32</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04374999999999979</v>
+        <v>0.02999999999999975</v>
       </c>
       <c r="N5" t="n">
-        <v>8.234999999999999</v>
+        <v>8.287500000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.58</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.07000000000000021</v>
+        <v>-0.08000000000000021</v>
       </c>
       <c r="N6" t="n">
-        <v>5.827500000000001</v>
+        <v>5.757500000000002</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.22</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1350000000000002</v>
+        <v>-0.1075000000000002</v>
       </c>
       <c r="N7" t="n">
-        <v>2.7175</v>
+        <v>2.571250000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.32</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1750000000000002</v>
+        <v>-0.1637500000000002</v>
       </c>
       <c r="N8" t="n">
-        <v>1.15625</v>
+        <v>1.078750000000002</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>-0.2262500000000002</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.067499999999999</v>
+        <v>-2.067499999999998</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1772,10 +1772,10 @@
         <v>0.01</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3762500000000002</v>
+        <v>-0.3762500000000003</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.3075</v>
+        <v>-3.307499999999999</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>-0.5212500000000002</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.72</v>
+        <v>-5.719999999999999</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2029,7 +2029,7 @@
         <v>-0.3887500000000003</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5987499999999994</v>
+        <v>-0.5987499999999986</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9832,6 +9832,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>472</v>
+      </c>
+      <c r="D75" t="n">
+        <v>393</v>
+      </c>
+      <c r="E75" t="n">
+        <v>78</v>
+      </c>
+      <c r="F75" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="G75" t="n">
+        <v>49</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.33%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J75" t="n">
+        <v>42</v>
+      </c>
+      <c r="K75" t="n">
+        <v>42</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.1399999999999997</v>
+      </c>
+      <c r="N75" t="n">
+        <v>16.115</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.6199999999999974</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03600464576074314</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.4200000000000017</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.02595797280593337</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
